--- a/excel/testdata/schema_data/data-mixed-types/workbook.xlsx
+++ b/excel/testdata/schema_data/data-mixed-types/workbook.xlsx
@@ -49,15 +49,20 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,13 +70,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9E9E9E"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9E9E9E"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9E9E9E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9E9E9E"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
   </cellXfs>
@@ -345,46 +370,46 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>21</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="3">
         <v>45352</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>31.5</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="3">
         <v>45353</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>42</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="3">
         <v>45354</v>
       </c>
     </row>

--- a/excel/testdata/schema_data/data-mixed-types/workbook.xlsx
+++ b/excel/testdata/schema_data/data-mixed-types/workbook.xlsx
@@ -43,10 +43,10 @@
   </numFmts>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
